--- a/assets/constructions/examples/ctd_mis_gears.xlsx
+++ b/assets/constructions/examples/ctd_mis_gears.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,11 +524,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GMGD10SD335-100-2U</t>
+          <t>GMGD8SD354-100-3U</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,7 +562,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>85.09</v>
+        <v>90</v>
       </c>
       <c r="E2" t="n">
         <v>25.4</v>
@@ -557,17 +577,17 @@
         <v>25</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2U</t>
+          <t>3U</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -577,7 +597,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>VARGUS_1/4U_GM</t>
+          <t>VARGUS_3/8U_GM</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -590,6 +610,20 @@
         <is>
           <t>2021 / NPA 56 Gear_Milling_Expanded Line INCH.pdf</t>
         </is>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1765.72</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>155176.06</v>
       </c>
     </row>
     <row r="3">
@@ -658,6 +692,20 @@
           <t>2022/VARGUS Обработка шлицев и зубчатых колёс</t>
         </is>
       </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1375.48</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>120880.76</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -725,11 +773,25 @@
           <t>2022/VARGUS Обработка шлицев и зубчатых колёс</t>
         </is>
       </c>
+      <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1186.54</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>104276.22</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GMGD8SD354-100-3U</t>
+          <t>GMGD10SD335-100-2U</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -743,7 +805,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>90</v>
+        <v>85.09</v>
       </c>
       <c r="E5" t="n">
         <v>25.4</v>
@@ -758,17 +820,17 @@
         <v>25</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>3U</t>
+          <t>2U</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -778,7 +840,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>VARGUS_3/8U_GM</t>
+          <t>VARGUS_1/4U_GM</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -791,6 +853,20 @@
         <is>
           <t>2021 / NPA 56 Gear_Milling_Expanded Line INCH.pdf</t>
         </is>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1523.88</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>133922.54</v>
       </c>
     </row>
   </sheetData>
